--- a/excel_config/indir/装备.xlsx
+++ b/excel_config/indir/装备.xlsx
@@ -743,12 +743,12 @@
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>string[]</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>json</t>
+          <t>string</t>
         </is>
       </c>
     </row>
@@ -793,12 +793,12 @@
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>["magic","lightning"]</t>
+          <t>magic:lightning</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>[{"type":"damage","damage_type":"magic","value":18,"scaling":{"magic_atk":1.8},"target":"enemy"}]</t>
+          <t>[{"type": "damage", "damage_type": "magic", "value": 18, "scaling": {"magic_atk": 1.8}, "target": "enemy"}]</t>
         </is>
       </c>
     </row>
@@ -829,12 +829,12 @@
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>["magic","shield","ice"]</t>
+          <t>magic:shield:ice</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>[{"type":"shield","value":12,"scaling":{"magic_atk":0.9},"target":"self"}]</t>
+          <t>[{"type": "shield", "value": 12, "scaling": {"magic_atk": 0.9}, "target": "self"}]</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>["magic","fire","control"]</t>
+          <t>magic:fire:control</t>
         </is>
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
-          <t>[{"type":"damage","damage_type":"magic","value":8,"scaling":{"magic_atk":0.8},"target":"enemy"},{"type":"buff","modifiers":{"buff_dot":1},"control":true,"control_chance":0.75,"target":"enemy"}]</t>
+          <t>[{"type": "damage", "damage_type": "magic", "value": 8, "scaling": {"magic_atk": 0.8}, "target": "enemy"}, {"type": "buff", "modifiers": {"buff_dot": 1}, "control": true, "control_chance": 0.75, "target": "enemy"}]</t>
         </is>
       </c>
     </row>
